--- a/src/main/java/resources/projects.xlsx
+++ b/src/main/java/resources/projects.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Java\projectStart\projectStart\src\main\java\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF5B50A-CFA6-4BA0-8606-EA6F3C01BAF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D55DC8A-3D47-4E56-B3A5-490CBD515140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,40 +27,40 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>dateStart</t>
+  </si>
+  <si>
+    <t>dateFinish</t>
+  </si>
+  <si>
+    <t>userId</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Artemon</t>
+  </si>
+  <si>
+    <t>Pelmen</t>
+  </si>
+  <si>
+    <t>Купить пудинг</t>
+  </si>
+  <si>
+    <t>Устроить марафон</t>
+  </si>
+  <si>
+    <t>Съездить в путеiествие</t>
+  </si>
+  <si>
     <t>id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>dateStart</t>
-  </si>
-  <si>
-    <t>dateFinish</t>
-  </si>
-  <si>
-    <t>userId</t>
-  </si>
-  <si>
-    <t>John</t>
-  </si>
-  <si>
-    <t>Artemon</t>
-  </si>
-  <si>
-    <t>Pelmen</t>
-  </si>
-  <si>
-    <t>Купить пудинг</t>
-  </si>
-  <si>
-    <t>Устроить марафон</t>
-  </si>
-  <si>
-    <t>Съездить в путеiествие</t>
   </si>
 </sst>
 </file>
@@ -389,22 +389,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -412,10 +412,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1">
         <v>43831</v>
@@ -432,10 +432,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1">
         <v>36588</v>
@@ -452,10 +452,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D4" s="1">
         <v>40461</v>
